--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.45768661413285</v>
+        <v>9.011874074796587</v>
       </c>
       <c r="D2" t="n">
-        <v>45.77390086064329</v>
+        <v>7.438258889854534</v>
       </c>
       <c r="E2" t="n">
-        <v>15.2907829136709</v>
+        <v>2.484752223471522</v>
       </c>
       <c r="F2" t="n">
-        <v>15.1784314892048</v>
+        <v>2.466495116995781</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.793540719929538</v>
+        <v>1.42895036698855</v>
       </c>
       <c r="D3" t="n">
-        <v>8.311577329303383</v>
+        <v>1.3506313160118</v>
       </c>
       <c r="E3" t="n">
-        <v>15.2907829136709</v>
+        <v>2.484752223471522</v>
       </c>
       <c r="F3" t="n">
-        <v>15.1784314892048</v>
+        <v>2.466495116995781</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.77749373427535</v>
+        <v>5.326342731819744</v>
       </c>
       <c r="D4" t="n">
-        <v>22.45551157288562</v>
+        <v>3.649020630593913</v>
       </c>
       <c r="E4" t="n">
-        <v>15.2907829136709</v>
+        <v>2.484752223471522</v>
       </c>
       <c r="F4" t="n">
-        <v>15.1784314892048</v>
+        <v>2.466495116995781</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.48152425594</v>
+        <v>6.740747691590251</v>
       </c>
       <c r="D5" t="n">
-        <v>42.41057024775685</v>
+        <v>6.891717665260488</v>
       </c>
       <c r="E5" t="n">
-        <v>15.2907829136709</v>
+        <v>2.484752223471522</v>
       </c>
       <c r="F5" t="n">
-        <v>15.1784314892048</v>
+        <v>2.466495116995781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.56902367093192</v>
+        <v>6.917466346526437</v>
       </c>
       <c r="D6" t="n">
-        <v>43.1274253903458</v>
+        <v>7.008206625931193</v>
       </c>
       <c r="E6" t="n">
-        <v>15.2907829136709</v>
+        <v>2.484752223471522</v>
       </c>
       <c r="F6" t="n">
-        <v>15.1784314892048</v>
+        <v>2.466495116995781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.73504818284565</v>
+        <v>8.406945329712418</v>
       </c>
       <c r="D7" t="n">
-        <v>51.67241950407371</v>
+        <v>8.396768169411978</v>
       </c>
       <c r="E7" t="n">
-        <v>15.2907829136709</v>
+        <v>2.484752223471522</v>
       </c>
       <c r="F7" t="n">
-        <v>15.1784314892048</v>
+        <v>2.466495116995781</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
